--- a/verification/cases/roundtrip/unicode_sheet_name/init.xlsx
+++ b/verification/cases/roundtrip/unicode_sheet_name/init.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="17127"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\test_library_java\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\frl\AppData\Local\Temp\xlsx-export-inits-3946636136\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8227AB7-B4A3-44F4-ADC1-9990B75E4B72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="11370"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet・1" sheetId="1" r:id="rId1"/>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -372,51 +373,51 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:A9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>4</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>6</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>7</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>9</v>
       </c>
